--- a/samples/sample2/Card_Payments.xlsx
+++ b/samples/sample2/Card_Payments.xlsx
@@ -66,9 +66,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -634,9 +635,763 @@
         <v>46218</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CA-T08</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Unit Testing</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Unit test – tokenisation service</v>
+      </c>
+      <c r="E10" t="str">
+        <v>2</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G10" t="str">
+        <v>90</v>
+      </c>
+      <c r="H10" s="2">
+        <v>46141</v>
+      </c>
+      <c r="I10" s="2">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CA-T09</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Unit Testing</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Unit test – fraud velocity rules</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G11" t="str">
+        <v>85</v>
+      </c>
+      <c r="H11" s="2">
+        <v>46141</v>
+      </c>
+      <c r="I11" s="2">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CA-T10</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Unit Testing</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Unit test – chargeback workflow</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G12" t="str">
+        <v>75</v>
+      </c>
+      <c r="H12" s="2">
+        <v>46148</v>
+      </c>
+      <c r="I12" s="2">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CA-T11</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Unit Testing</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Unit test – acquiring settlement</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G13" t="str">
+        <v>65</v>
+      </c>
+      <c r="H13" s="2">
+        <v>46148</v>
+      </c>
+      <c r="I13" s="2">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CA-T12</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Unit Testing</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Unit test sign-off</v>
+      </c>
+      <c r="E14" t="str">
+        <v>1</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G14" t="str">
+        <v>50</v>
+      </c>
+      <c r="H14" s="2">
+        <v>46155</v>
+      </c>
+      <c r="I14" s="2">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CA-T13</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Unit Testing</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Code coverage review</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G15" t="str">
+        <v>40</v>
+      </c>
+      <c r="H15" s="2">
+        <v>46157</v>
+      </c>
+      <c r="I15" s="2">
+        <v>46162</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CA-T14</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C16" t="str">
+        <v>SIT</v>
+      </c>
+      <c r="D16" t="str">
+        <v>SIT – fraud rules engine</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G16" t="str">
+        <v>15</v>
+      </c>
+      <c r="H16" s="2">
+        <v>46176</v>
+      </c>
+      <c r="I16" s="2">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CA-T15</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C17" t="str">
+        <v>SIT</v>
+      </c>
+      <c r="D17" t="str">
+        <v>SIT – chargeback &amp; dispute flow</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G17" t="str">
+        <v>10</v>
+      </c>
+      <c r="H17" s="2">
+        <v>46183</v>
+      </c>
+      <c r="I17" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CA-T16</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C18" t="str">
+        <v>SIT</v>
+      </c>
+      <c r="D18" t="str">
+        <v>SIT – PCI-DSS compliance check</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G18" t="str">
+        <v>5</v>
+      </c>
+      <c r="H18" s="2">
+        <v>46190</v>
+      </c>
+      <c r="I18" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>CA-T17</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C19" t="str">
+        <v>SIT</v>
+      </c>
+      <c r="D19" t="str">
+        <v>SIT defect triage &amp; retest</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G19" t="str">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>46197</v>
+      </c>
+      <c r="I19" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>CA-T18</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C20" t="str">
+        <v>SIT</v>
+      </c>
+      <c r="D20" t="str">
+        <v>SIT closure report</v>
+      </c>
+      <c r="E20" t="str">
+        <v>1</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G20" t="str">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>46211</v>
+      </c>
+      <c r="I20" s="2">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>CA-T19</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C21" t="str">
+        <v>SIT</v>
+      </c>
+      <c r="D21" t="str">
+        <v>SIT sign-off</v>
+      </c>
+      <c r="E21" t="str">
+        <v>1</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G21" t="str">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>46213</v>
+      </c>
+      <c r="I21" s="2">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>CA-T20</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Performance test plan &amp; environment</v>
+      </c>
+      <c r="E22" t="str">
+        <v>1</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="G22" t="str">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>46169</v>
+      </c>
+      <c r="I22" s="2">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>CA-T21</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Baseline test – card authorisation</v>
+      </c>
+      <c r="E23" t="str">
+        <v>2</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="G23" t="str">
+        <v>5</v>
+      </c>
+      <c r="H23" s="2">
+        <v>46183</v>
+      </c>
+      <c r="I23" s="2">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>CA-T22</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Soak test – 48hr card auth</v>
+      </c>
+      <c r="E24" t="str">
+        <v>2</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="G24" t="str">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>46190</v>
+      </c>
+      <c r="I24" s="2">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>CA-T23</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Stress test – peak TPS (800 TPS)</v>
+      </c>
+      <c r="E25" t="str">
+        <v>2</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="G25" t="str">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>46197</v>
+      </c>
+      <c r="I25" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>CA-T24</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Bottleneck analysis &amp; tuning</v>
+      </c>
+      <c r="E26" t="str">
+        <v>2</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="G26" t="str">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>46204</v>
+      </c>
+      <c r="I26" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>CA-T25</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Performance test sign-off</v>
+      </c>
+      <c r="E27" t="str">
+        <v>1</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="G27" t="str">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>46218</v>
+      </c>
+      <c r="I27" s="2">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>CA-T26</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Performance closure report</v>
+      </c>
+      <c r="E28" t="str">
+        <v>1</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="G28" t="str">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>46220</v>
+      </c>
+      <c r="I28" s="2">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>CA-T27</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C29" t="str">
+        <v>UAT</v>
+      </c>
+      <c r="D29" t="str">
+        <v>UAT plan &amp; business user training</v>
+      </c>
+      <c r="E29" t="str">
+        <v>1</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G29" t="str">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>46204</v>
+      </c>
+      <c r="I29" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>CA-T28</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C30" t="str">
+        <v>UAT</v>
+      </c>
+      <c r="D30" t="str">
+        <v>UAT – issuing positive flow</v>
+      </c>
+      <c r="E30" t="str">
+        <v>2</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G30" t="str">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>46218</v>
+      </c>
+      <c r="I30" s="2">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>CA-T29</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C31" t="str">
+        <v>UAT</v>
+      </c>
+      <c r="D31" t="str">
+        <v>UAT – acquiring &amp; merchant scenarios</v>
+      </c>
+      <c r="E31" t="str">
+        <v>2</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G31" t="str">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2">
+        <v>46225</v>
+      </c>
+      <c r="I31" s="2">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>CA-T30</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C32" t="str">
+        <v>UAT</v>
+      </c>
+      <c r="D32" t="str">
+        <v>UAT – fraud &amp; dispute scenarios</v>
+      </c>
+      <c r="E32" t="str">
+        <v>2</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G32" t="str">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>46232</v>
+      </c>
+      <c r="I32" s="2">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>CA-T31</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C33" t="str">
+        <v>UAT</v>
+      </c>
+      <c r="D33" t="str">
+        <v>UAT – chargeback &amp; recovery</v>
+      </c>
+      <c r="E33" t="str">
+        <v>2</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G33" t="str">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2">
+        <v>46239</v>
+      </c>
+      <c r="I33" s="2">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>CA-T32</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C34" t="str">
+        <v>UAT</v>
+      </c>
+      <c r="D34" t="str">
+        <v>UAT defect resolution &amp; retest</v>
+      </c>
+      <c r="E34" t="str">
+        <v>2</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G34" t="str">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2">
+        <v>46246</v>
+      </c>
+      <c r="I34" s="2">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>CA-T33</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Card Payments</v>
+      </c>
+      <c r="C35" t="str">
+        <v>UAT</v>
+      </c>
+      <c r="D35" t="str">
+        <v>UAT closure &amp; sign-off</v>
+      </c>
+      <c r="E35" t="str">
+        <v>1</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G35" t="str">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2">
+        <v>46260</v>
+      </c>
+      <c r="I35" s="2">
+        <v>46262</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I35"/>
   </ignoredErrors>
 </worksheet>
 </file>
